--- a/automotive_forms/017_engine_performance_assessment--automotive_forms.xlsx
+++ b/automotive_forms/017_engine_performance_assessment--automotive_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'bad',_'value':_1}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Bad', 'value': 1}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fair',_'value':_2}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fair', 'value': 2}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'good',_'value':_3}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Good', 'value': 3}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'excellent',_'value':_4}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Excellent', 'value': 4}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'low',_'value':_1}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Low', 'value': 1}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium',_'value':_2}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium', 'value': 2}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'high',_'value':_3}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'High', 'value': 3}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'empty',_'value':_1}</t>
+          <t>empty</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Empty', 'value': 1}</t>
+          <t>Empty</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'less_than_1/4',_'value':_2}</t>
+          <t>less_than_1/4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Less than 1/4', 'value': 2}</t>
+          <t>Less than 1/4</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'1/4_to_1/2',_'value':_3}</t>
+          <t>1/4_to_1/2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '1/4 to 1/2', 'value': 3}</t>
+          <t>1/4 to 1/2</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'1/2_to_3/4',_'value':_4}</t>
+          <t>1/2_to_3/4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '1/2 to 3/4', 'value': 4}</t>
+          <t>1/2 to 3/4</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'more_than_3/4',_'value':_5}</t>
+          <t>more_than_3/4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'More than 3/4', 'value': 5}</t>
+          <t>More than 3/4</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'low_oil_level',_'value':_1}</t>
+          <t>low_oil_level</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Low Oil Level', 'value': 1}</t>
+          <t>Low Oil Level</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'high_water_temperature',_'value':_2}</t>
+          <t>high_water_temperature</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'High Water Temperature', 'value': 2}</t>
+          <t>High Water Temperature</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'leaking_oil',_'value':_3}</t>
+          <t>leaking_oil</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Leaking Oil', 'value': 3}</t>
+          <t>Leaking Oil</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'overheating',_'value':_4}</t>
+          <t>overheating</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Overheating', 'value': 4}</t>
+          <t>Overheating</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other_(please_specify)',_'value':_5}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other (please specify)', 'value': 5}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'no_problem',_'value':_6}</t>
+          <t>no_problem</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'No Problem', 'value': 6}</t>
+          <t>No Problem</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'regular',_'value':_1}</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Regular', 'value': 1}</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'mid-grade',_'value':_2}</t>
+          <t>mid-grade</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Mid-Grade', 'value': 2}</t>
+          <t>Mid-Grade</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'premium',_'value':_3}</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Premium', 'value': 3}</t>
+          <t>Premium</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'diesel',_'value':_4}</t>
+          <t>diesel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Diesel', 'value': 4}</t>
+          <t>Diesel</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other_(please_specify)',_'value':_5}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other (please specify)', 'value': 5}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'gas',_'value':_1}</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Gas', 'value': 1}</t>
+          <t>Gas</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'diesel',_'value':_2}</t>
+          <t>diesel</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Diesel', 'value': 2}</t>
+          <t>Diesel</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'hybrid',_'value':_3}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Hybrid', 'value': 3}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other_(please_specify)',_'value':_4}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other (please specify)', 'value': 4}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'clean',_'value':_1}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Clean', 'value': 1}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'dirty',_'value':_2}</t>
+          <t>dirty</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Dirty', 'value': 2}</t>
+          <t>Dirty</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_installed',_'value':_3}</t>
+          <t>not_installed</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Installed', 'value': 3}</t>
+          <t>Not Installed</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other_(please_specify)',_'value':_4}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other (please specify)', 'value': 4}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'clean',_'value':_1}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Clean', 'value': 1}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'dirty',_'value':_2}</t>
+          <t>dirty</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Dirty', 'value': 2}</t>
+          <t>Dirty</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_installed',_'value':_3}</t>
+          <t>not_installed</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Installed', 'value': 3}</t>
+          <t>Not Installed</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other_(please_specify)',_'value':_4}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other (please specify)', 'value': 4}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'automatic',_'value':_1}</t>
+          <t>automatic</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Automatic', 'value': 1}</t>
+          <t>Automatic</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'manual',_'value':_2}</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Manual', 'value': 2}</t>
+          <t>Manual</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'semi-automatic',_'value':_3}</t>
+          <t>semi-automatic</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Semi-Automatic', 'value': 3}</t>
+          <t>Semi-Automatic</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'cvt',_'value':_4}</t>
+          <t>cvt</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'CVT', 'value': 4}</t>
+          <t>CVT</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other_(please_specify)',_'value':_5}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other (please specify)', 'value': 5}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'low',_'value':_1}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Low', 'value': 1}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium',_'value':_2}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium', 'value': 2}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'high',_'value':_3}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'High', 'value': 3}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'excellent',_'value':_4}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Excellent', 'value': 4}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'clean',_'value':_1}</t>
+          <t>clean</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Clean', 'value': 1}</t>
+          <t>Clean</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'dirty',_'value':_2}</t>
+          <t>dirty</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Dirty', 'value': 2}</t>
+          <t>Dirty</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_installed',_'value':_3}</t>
+          <t>not_installed</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Installed', 'value': 3}</t>
+          <t>Not Installed</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other_(please_specify)',_'value':_4}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other (please specify)', 'value': 4}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'front-wheel_drive',_'value':_1}</t>
+          <t>front-wheel_drive</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Front-Wheel Drive', 'value': 1}</t>
+          <t>Front-Wheel Drive</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'rear-wheel_drive',_'value':_2}</t>
+          <t>rear-wheel_drive</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Rear-Wheel Drive', 'value': 2}</t>
+          <t>Rear-Wheel Drive</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'all-wheel_drive',_'value':_3}</t>
+          <t>all-wheel_drive</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'All-Wheel Drive', 'value': 3}</t>
+          <t>All-Wheel Drive</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'four-wheel_drive',_'value':_4}</t>
+          <t>four-wheel_drive</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Four-Wheel Drive', 'value': 4}</t>
+          <t>Four-Wheel Drive</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other_(please_specify)',_'value':_5}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other (please specify)', 'value': 5}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_false,_'value':_1}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': False, 'value': 1}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_true,_'value':_2}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': True, 'value': 2}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other_(please_specify)',_'value':_3}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other (please specify)', 'value': 3}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'new',_'value':_1}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'New', 'value': 1}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'average',_'value':_2}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Average', 'value': 2}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'used',_'value':_3}</t>
+          <t>used</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Used', 'value': 3}</t>
+          <t>Used</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other_(please_specify)',_'value':_4}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other (please specify)', 'value': 4}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
